--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414786</v>
       </c>
       <c r="B2" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97321</v>
+        <v>97325</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414782</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -991,6 +991,550 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127713889</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91102</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Acksjön, Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>636783</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6553343</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127713928</v>
+      </c>
+      <c r="B6" t="n">
+        <v>97325</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Acksjön, Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>636784</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6553330</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127713555</v>
+      </c>
+      <c r="B7" t="n">
+        <v>92612</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stora Dröpplan, Stora Dröpplan, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>636829</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6553187</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127713802</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97328</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Acksjön, Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>636805</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6553291</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127714276</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91102</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Acksjön, Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>636859</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6553276</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:04</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414786</v>
       </c>
       <c r="B2" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97325</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414782</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B5" t="n">
-        <v>91102</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R5" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B6" t="n">
-        <v>97325</v>
+        <v>91104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R6" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92612</v>
+        <v>92614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97328</v>
+        <v>97330</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91102</v>
+        <v>91104</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>91104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R5" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>91104</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R6" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B5" t="n">
-        <v>91104</v>
+        <v>97327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R5" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>91104</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R6" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>97333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>97327</v>
+        <v>91110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R5" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>91104</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R6" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97330</v>
+        <v>97336</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91104</v>
+        <v>91110</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414786</v>
       </c>
       <c r="B2" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414782</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>97336</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97336</v>
+        <v>97339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127414786</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97336</v>
+        <v>97344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>127414782</v>
       </c>
       <c r="B4" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B5" t="n">
-        <v>91113</v>
+        <v>97344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R5" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B6" t="n">
-        <v>97336</v>
+        <v>91121</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R6" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97339</v>
+        <v>97347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91113</v>
+        <v>91121</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97344</v>
+        <v>97345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>97344</v>
+        <v>91122</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R5" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>91121</v>
+        <v>97345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R6" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97347</v>
+        <v>97348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91121</v>
+        <v>91122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>97345</v>
+        <v>97346</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97348</v>
+        <v>97349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91122</v>
+        <v>91123</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>127414785</v>
       </c>
       <c r="B3" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>97346</v>
+        <v>97347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97349</v>
+        <v>97350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91123</v>
+        <v>91124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B5" t="n">
-        <v>91124</v>
+        <v>97347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R5" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B6" t="n">
-        <v>97347</v>
+        <v>91124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R6" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -996,7 +996,7 @@
         <v>127713928</v>
       </c>
       <c r="B5" t="n">
-        <v>97347</v>
+        <v>97355</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1103,7 +1103,7 @@
         <v>127713889</v>
       </c>
       <c r="B6" t="n">
-        <v>91124</v>
+        <v>91133</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97350</v>
+        <v>97358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91124</v>
+        <v>91133</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713928</v>
+        <v>127713889</v>
       </c>
       <c r="B5" t="n">
-        <v>97355</v>
+        <v>91144</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,21 +1004,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636784</v>
+        <v>636783</v>
       </c>
       <c r="R5" t="n">
-        <v>6553330</v>
+        <v>6553343</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1073,7 +1073,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:41</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1100,10 +1100,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713889</v>
+        <v>127713928</v>
       </c>
       <c r="B6" t="n">
-        <v>91133</v>
+        <v>97367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,21 +1111,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636783</v>
+        <v>636784</v>
       </c>
       <c r="R6" t="n">
-        <v>6553343</v>
+        <v>6553330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,7 +1210,7 @@
         <v>127713555</v>
       </c>
       <c r="B7" t="n">
-        <v>92642</v>
+        <v>92653</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,7 +1326,7 @@
         <v>127713802</v>
       </c>
       <c r="B8" t="n">
-        <v>97358</v>
+        <v>97370</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>127714276</v>
       </c>
       <c r="B9" t="n">
-        <v>91133</v>
+        <v>91144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127414786</v>
+        <v>127713889</v>
       </c>
       <c r="B2" t="n">
-        <v>57669</v>
+        <v>91680</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>3215</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Molstaberg, Srm</t>
+          <t>Acksjön, Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>636818</v>
+        <v>636783</v>
       </c>
       <c r="R2" t="n">
-        <v>6553171</v>
+        <v>6553343</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,17 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127414785</v>
+        <v>127714276</v>
       </c>
       <c r="B3" t="n">
-        <v>97347</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,41 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Molstaberg, Srm</t>
+          <t>Acksjön, Acksjön, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>636843</v>
+        <v>636859</v>
       </c>
       <c r="R3" t="n">
-        <v>6553157</v>
+        <v>6553276</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -850,17 +847,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127414782</v>
+        <v>127713555</v>
       </c>
       <c r="B4" t="n">
-        <v>57669</v>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -898,41 +900,46 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Molstaberg, Srm</t>
+          <t>Stora Dröpplan, Stora Dröpplan, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>636866</v>
+        <v>636829</v>
       </c>
       <c r="R4" t="n">
-        <v>6553200</v>
+        <v>6553187</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -956,17 +963,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-01</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>08:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,22 +993,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Gustaf Eibl</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127713889</v>
+        <v>127414782</v>
       </c>
       <c r="B5" t="n">
-        <v>91144</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1004,37 +1016,41 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3215</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Acksjön, Acksjön, Srm</t>
+          <t>Molstaberg, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>636783</v>
+        <v>636866</v>
       </c>
       <c r="R5" t="n">
-        <v>6553343</v>
+        <v>6553200</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1058,22 +1074,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>08:39</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>08:39</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,22 +1099,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127713928</v>
+        <v>127414786</v>
       </c>
       <c r="B6" t="n">
-        <v>97367</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1111,37 +1122,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Acksjön, Acksjön, Srm</t>
+          <t>Molstaberg, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>636784</v>
+        <v>636818</v>
       </c>
       <c r="R6" t="n">
-        <v>6553330</v>
+        <v>6553171</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,22 +1180,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,66 +1205,57 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127713555</v>
+        <v>127713301</v>
       </c>
       <c r="B7" t="n">
-        <v>92653</v>
+        <v>99035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Stora Dröpplan, Stora Dröpplan, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>636829</v>
+        <v>636873</v>
       </c>
       <c r="R7" t="n">
-        <v>6553187</v>
+        <v>6553165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1287,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1296,7 +1297,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:05</t>
+          <t>07:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1323,10 +1324,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127713802</v>
+        <v>127414785</v>
       </c>
       <c r="B8" t="n">
-        <v>97370</v>
+        <v>97983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1334,16 +1335,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1351,20 +1352,24 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Acksjön, Acksjön, Srm</t>
+          <t>Molstaberg, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>636805</v>
+        <v>636843</v>
       </c>
       <c r="R8" t="n">
-        <v>6553291</v>
+        <v>6553157</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1388,22 +1393,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>08:32</t>
+          <t>2025-08-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>08:32</t>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1418,22 +1418,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gustaf Eibl</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127714276</v>
+        <v>127713311</v>
       </c>
       <c r="B9" t="n">
-        <v>91144</v>
+        <v>97983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1441,34 +1441,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3215</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Acksjön, Acksjön, Srm</t>
+          <t>Stora Dröpplan, Stora Dröpplan, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>636859</v>
+        <v>636872</v>
       </c>
       <c r="R9" t="n">
-        <v>6553276</v>
+        <v>6553165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1500,7 +1500,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1534,6 +1534,327 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127713928</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Acksjön, Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>636784</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6553330</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>08:41</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127713257</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Stora Dröpplan, Stora Dröpplan, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>636888</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6553162</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>07:40</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127713802</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Acksjön, Acksjön, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>636805</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6553291</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-08-21</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36854-2025 artfynd.xlsx
+++ b/artfynd/A 36854-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713889</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127714276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713555</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414782</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1214,6 +1239,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414786</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1321,6 +1351,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713301</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1427,6 +1462,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127414785</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1534,6 +1574,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713311</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1641,6 +1686,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713928</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1748,6 +1798,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1855,8 +1910,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127713802</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>